--- a/MAJSushiConfig/ig/StructureDefinition-fr-medication-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-medication-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -678,7 +678,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-medication-translation-document|0.1.0</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -772,7 +772,7 @@
     <t>When Medication is referenced from MedicationRequest, this is the ordered form.  When Medication is referenced within MedicationDispense, this is the dispensed form.  When Medication is referenced within MedicationAdministration, this is administered form.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-edqm-form-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-edqm-form-document|0.1.0</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -918,7 +918,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1407,7 +1407,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="47.4921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="87.83203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="84.6328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
